--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126953125</v>
       </c>
       <c r="B3" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126953125</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126953125</v>
       </c>
       <c r="B3" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126953125</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126953125</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126953125</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126953125</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118095036</v>
+        <v>126953125</v>
       </c>
       <c r="B2" t="n">
-        <v>44774</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208307</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pudrad kärrtrollslända</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucorrhinia albifrons</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Burmeister, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rogsån Jämtbo, Dlr</t>
+          <t>Jämtbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533838</v>
+        <v>533862</v>
       </c>
       <c r="R2" t="n">
-        <v>6729835</v>
+        <v>6729514</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,77 +770,88 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Omkring Rogsån</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126953125</v>
+        <v>118492435</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jämtbo, Dlr</t>
+          <t>Jämtbo N om, Jämtbo N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533862</v>
+        <v>533832</v>
       </c>
       <c r="R3" t="n">
-        <v>6729514</v>
+        <v>6729854</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,17 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,19 +899,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -892,6 +918,216 @@
           <t>Omkring Rogsån</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118116353</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45298</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208306</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bred kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucorrhinia caudalis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1840)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rogsån, Falun , Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>533845</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6729866</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Uno Skog, Holger Martinussen, Erik Danielsson, Evalena Sköld, Bo karlstens, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118095036</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45297</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208307</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pudrad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucorrhinia albifrons</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Burmeister, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rogsån Jämtbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533838</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6729835</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28119-2025 artfynd.xlsx
+++ b/artfynd/A 28119-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
           <t>Omkring Rogsån</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126953125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Omkring Rogsån</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118492435</t>
         </is>
       </c>
     </row>
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118116353</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,8 +1148,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118095036</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>